--- a/analises/2026-09-23-tanyno-tintos-chardonnay-preco-final.xlsx
+++ b/analises/2026-09-23-tanyno-tintos-chardonnay-preco-final.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Preço final" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Cartão 5x" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>Fator sobre A37</t>
   </si>
   <si>
-    <t>Simples Nacional (sobre a venda, no cálculo do preço de venda)</t>
+    <t>Simples Nacional (sobre a venda)</t>
   </si>
   <si>
     <t>Acréscimo sobre o preço de venda</t>
@@ -43,13 +43,10 @@
     <t>Markup</t>
   </si>
   <si>
-    <t>Preço de venda (custo × markup ÷ 0,92)</t>
-  </si>
-  <si>
     <t>Acréscimo 8%</t>
   </si>
   <si>
-    <t>Preço final (venda + 8%)</t>
+    <t>Cartão em até 5x sem juros</t>
   </si>
   <si>
     <t>Le Serre Nuove dell'Ornellaia magnum</t>
@@ -609,16 +606,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="5" max="6" width="17" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -645,7 +641,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -673,16 +669,13 @@
       <c r="I5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
       </c>
       <c r="C6" s="4">
         <v>2022</v>
@@ -701,24 +694,20 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="5">
-        <f>F6*G6/(1-$B$2)</f>
-        <v>2588.136953804347</v>
-      </c>
-      <c r="I6" s="5">
-        <f>H6*$B$3</f>
+        <f>F6*G6/(1-$B$2)*$B$3</f>
         <v>207.05095630434775</v>
       </c>
-      <c r="J6" s="7">
-        <f>H6+I6</f>
+      <c r="I6" s="7">
+        <f>F6*G6/(1-$B$2)*(1+$B$3)</f>
         <v>2795.1879101086947</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>16</v>
       </c>
       <c r="C7" s="9">
         <v>2021</v>
@@ -737,24 +726,20 @@
         <v>1.4</v>
       </c>
       <c r="H7" s="10">
-        <f>F7*G7/(1-$B$2)</f>
-        <v>2715.927646630434</v>
-      </c>
-      <c r="I7" s="10">
-        <f>H7*$B$3</f>
+        <f>F7*G7/(1-$B$2)*$B$3</f>
         <v>217.27421173043473</v>
       </c>
-      <c r="J7" s="12">
-        <f>H7+I7</f>
+      <c r="I7" s="12">
+        <f>F7*G7/(1-$B$2)*(1+$B$3)</f>
         <v>2933.201858360869</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
       </c>
       <c r="C8" s="4">
         <v>2023</v>
@@ -773,24 +758,20 @@
         <v>1.4</v>
       </c>
       <c r="H8" s="5">
-        <f>F8*G8/(1-$B$2)</f>
-        <v>2731.420757282608</v>
-      </c>
-      <c r="I8" s="5">
-        <f>H8*$B$3</f>
+        <f>F8*G8/(1-$B$2)*$B$3</f>
         <v>218.51366058260865</v>
       </c>
-      <c r="J8" s="7">
-        <f>H8+I8</f>
+      <c r="I8" s="7">
+        <f>F8*G8/(1-$B$2)*(1+$B$3)</f>
         <v>2949.934417865217</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="9">
         <v>2023</v>
@@ -809,24 +790,20 @@
         <v>1.4</v>
       </c>
       <c r="H9" s="10">
-        <f>F9*G9/(1-$B$2)</f>
-        <v>2731.420757282608</v>
-      </c>
-      <c r="I9" s="10">
-        <f>H9*$B$3</f>
+        <f>F9*G9/(1-$B$2)*$B$3</f>
         <v>218.51366058260865</v>
       </c>
-      <c r="J9" s="12">
-        <f>H9+I9</f>
+      <c r="I9" s="12">
+        <f>F9*G9/(1-$B$2)*(1+$B$3)</f>
         <v>2949.934417865217</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
       </c>
       <c r="C10" s="4">
         <v>2023</v>
@@ -845,24 +822,20 @@
         <v>1.4</v>
       </c>
       <c r="H10" s="5">
-        <f>F10*G10/(1-$B$2)</f>
-        <v>2926.421516413043</v>
-      </c>
-      <c r="I10" s="5">
-        <f>H10*$B$3</f>
+        <f>F10*G10/(1-$B$2)*$B$3</f>
         <v>234.11372131304344</v>
       </c>
-      <c r="J10" s="7">
-        <f>H10+I10</f>
+      <c r="I10" s="7">
+        <f>F10*G10/(1-$B$2)*(1+$B$3)</f>
         <v>3160.5352377260865</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="C11" s="9">
         <v>2022</v>
@@ -881,24 +854,20 @@
         <v>1.4</v>
       </c>
       <c r="H11" s="10">
-        <f>F11*G11/(1-$B$2)</f>
-        <v>3027.236615869564</v>
-      </c>
-      <c r="I11" s="10">
-        <f>H11*$B$3</f>
+        <f>F11*G11/(1-$B$2)*$B$3</f>
         <v>242.17892926956512</v>
       </c>
-      <c r="J11" s="12">
-        <f>H11+I11</f>
+      <c r="I11" s="12">
+        <f>F11*G11/(1-$B$2)*(1+$B$3)</f>
         <v>3269.4155451391293</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="4">
         <v>2002</v>
@@ -917,24 +886,20 @@
         <v>1.4</v>
       </c>
       <c r="H12" s="5">
-        <f>F12*G12/(1-$B$2)</f>
-        <v>3109.8665393478254</v>
-      </c>
-      <c r="I12" s="5">
-        <f>H12*$B$3</f>
+        <f>F12*G12/(1-$B$2)*$B$3</f>
         <v>248.78932314782605</v>
       </c>
-      <c r="J12" s="7">
-        <f>H12+I12</f>
+      <c r="I12" s="7">
+        <f>F12*G12/(1-$B$2)*(1+$B$3)</f>
         <v>3358.6558624956515</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="C13" s="9">
         <v>2022</v>
@@ -953,24 +918,20 @@
         <v>1.4</v>
       </c>
       <c r="H13" s="10">
-        <f>F13*G13/(1-$B$2)</f>
-        <v>3112.119083804347</v>
-      </c>
-      <c r="I13" s="10">
-        <f>H13*$B$3</f>
+        <f>F13*G13/(1-$B$2)*$B$3</f>
         <v>248.96952670434777</v>
       </c>
-      <c r="J13" s="12">
-        <f>H13+I13</f>
+      <c r="I13" s="12">
+        <f>F13*G13/(1-$B$2)*(1+$B$3)</f>
         <v>3361.088610508695</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
       </c>
       <c r="C14" s="4">
         <v>2023</v>
@@ -989,24 +950,20 @@
         <v>1.4</v>
       </c>
       <c r="H14" s="5">
-        <f>F14*G14/(1-$B$2)</f>
-        <v>3185.9952166304342</v>
-      </c>
-      <c r="I14" s="5">
-        <f>H14*$B$3</f>
+        <f>F14*G14/(1-$B$2)*$B$3</f>
         <v>254.87961733043474</v>
       </c>
-      <c r="J14" s="7">
-        <f>H14+I14</f>
+      <c r="I14" s="7">
+        <f>F14*G14/(1-$B$2)*(1+$B$3)</f>
         <v>3440.874833960869</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="C15" s="9">
         <v>2022</v>
@@ -1025,24 +982,20 @@
         <v>1.33</v>
       </c>
       <c r="H15" s="10">
-        <f>F15*G15/(1-$B$2)</f>
-        <v>3378.0594269510866</v>
-      </c>
-      <c r="I15" s="10">
-        <f>H15*$B$3</f>
+        <f>F15*G15/(1-$B$2)*$B$3</f>
         <v>270.2447541560869</v>
       </c>
-      <c r="J15" s="12">
-        <f>H15+I15</f>
+      <c r="I15" s="12">
+        <f>F15*G15/(1-$B$2)*(1+$B$3)</f>
         <v>3648.304181107174</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
       </c>
       <c r="C16" s="4">
         <v>2019</v>
@@ -1061,24 +1014,20 @@
         <v>1.33</v>
       </c>
       <c r="H16" s="5">
-        <f>F16*G16/(1-$B$2)</f>
-        <v>3463.8648887119557</v>
-      </c>
-      <c r="I16" s="5">
-        <f>H16*$B$3</f>
+        <f>F16*G16/(1-$B$2)*$B$3</f>
         <v>277.10919109695647</v>
       </c>
-      <c r="J16" s="7">
-        <f>H16+I16</f>
+      <c r="I16" s="7">
+        <f>F16*G16/(1-$B$2)*(1+$B$3)</f>
         <v>3740.9740798089124</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="9">
         <v>2022</v>
@@ -1097,24 +1046,20 @@
         <v>1.33</v>
       </c>
       <c r="H17" s="10">
-        <f>F17*G17/(1-$B$2)</f>
-        <v>3548.9048516249995</v>
-      </c>
-      <c r="I17" s="10">
-        <f>H17*$B$3</f>
+        <f>F17*G17/(1-$B$2)*$B$3</f>
         <v>283.91238812999995</v>
       </c>
-      <c r="J17" s="12">
-        <f>H17+I17</f>
+      <c r="I17" s="12">
+        <f>F17*G17/(1-$B$2)*(1+$B$3)</f>
         <v>3832.8172397549997</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
         <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
       </c>
       <c r="C18" s="4">
         <v>2023</v>
@@ -1133,24 +1078,20 @@
         <v>1.33</v>
       </c>
       <c r="H18" s="5">
-        <f>F18*G18/(1-$B$2)</f>
-        <v>3563.971260766304</v>
-      </c>
-      <c r="I18" s="5">
-        <f>H18*$B$3</f>
+        <f>F18*G18/(1-$B$2)*$B$3</f>
         <v>285.11770086130434</v>
       </c>
-      <c r="J18" s="7">
-        <f>H18+I18</f>
+      <c r="I18" s="7">
+        <f>F18*G18/(1-$B$2)*(1+$B$3)</f>
         <v>3849.0889616276086</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="9">
         <v>2022</v>
@@ -1169,24 +1110,20 @@
         <v>1.33</v>
       </c>
       <c r="H19" s="10">
-        <f>F19*G19/(1-$B$2)</f>
-        <v>3614.389798516305</v>
-      </c>
-      <c r="I19" s="10">
-        <f>H19*$B$3</f>
+        <f>F19*G19/(1-$B$2)*$B$3</f>
         <v>289.1511838813044</v>
       </c>
-      <c r="J19" s="12">
-        <f>H19+I19</f>
+      <c r="I19" s="12">
+        <f>F19*G19/(1-$B$2)*(1+$B$3)</f>
         <v>3903.5409823976097</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
         <v>36</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
       </c>
       <c r="C20" s="4">
         <v>2006</v>
@@ -1205,24 +1142,20 @@
         <v>1.33</v>
       </c>
       <c r="H20" s="5">
-        <f>F20*G20/(1-$B$2)</f>
-        <v>3877.7735952717385</v>
-      </c>
-      <c r="I20" s="5">
-        <f>H20*$B$3</f>
+        <f>F20*G20/(1-$B$2)*$B$3</f>
         <v>310.2218876217391</v>
       </c>
-      <c r="J20" s="7">
-        <f>H20+I20</f>
+      <c r="I20" s="7">
+        <f>F20*G20/(1-$B$2)*(1+$B$3)</f>
         <v>4187.995482893478</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="C21" s="9">
         <v>2016</v>
@@ -1241,24 +1174,20 @@
         <v>1.33</v>
       </c>
       <c r="H21" s="10">
-        <f>F21*G21/(1-$B$2)</f>
-        <v>3982.525153516304</v>
-      </c>
-      <c r="I21" s="10">
-        <f>H21*$B$3</f>
+        <f>F21*G21/(1-$B$2)*$B$3</f>
         <v>318.6020122813043</v>
       </c>
-      <c r="J21" s="12">
-        <f>H21+I21</f>
+      <c r="I21" s="12">
+        <f>F21*G21/(1-$B$2)*(1+$B$3)</f>
         <v>4301.1271657976085</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
         <v>40</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
       </c>
       <c r="C22" s="4">
         <v>2023</v>
@@ -1277,24 +1206,20 @@
         <v>1.33</v>
       </c>
       <c r="H22" s="5">
-        <f>F22*G22/(1-$B$2)</f>
-        <v>4080.2828359239134</v>
-      </c>
-      <c r="I22" s="5">
-        <f>H22*$B$3</f>
+        <f>F22*G22/(1-$B$2)*$B$3</f>
         <v>326.4226268739131</v>
       </c>
-      <c r="J22" s="7">
-        <f>H22+I22</f>
+      <c r="I22" s="7">
+        <f>F22*G22/(1-$B$2)*(1+$B$3)</f>
         <v>4406.705462797827</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9">
         <v>2022</v>
@@ -1313,24 +1238,20 @@
         <v>1.33</v>
       </c>
       <c r="H23" s="10">
-        <f>F23*G23/(1-$B$2)</f>
-        <v>4383.994503798913</v>
-      </c>
-      <c r="I23" s="10">
-        <f>H23*$B$3</f>
+        <f>F23*G23/(1-$B$2)*$B$3</f>
         <v>350.71956030391306</v>
       </c>
-      <c r="J23" s="12">
-        <f>H23+I23</f>
+      <c r="I23" s="12">
+        <f>F23*G23/(1-$B$2)*(1+$B$3)</f>
         <v>4734.714064102826</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="4">
         <v>2022</v>
@@ -1349,24 +1270,20 @@
         <v>1.33</v>
       </c>
       <c r="H24" s="5">
-        <f>F24*G24/(1-$B$2)</f>
-        <v>4752.634392130433</v>
-      </c>
-      <c r="I24" s="5">
-        <f>H24*$B$3</f>
+        <f>F24*G24/(1-$B$2)*$B$3</f>
         <v>380.21075137043465</v>
       </c>
-      <c r="J24" s="7">
-        <f>H24+I24</f>
+      <c r="I24" s="7">
+        <f>F24*G24/(1-$B$2)*(1+$B$3)</f>
         <v>5132.845143500868</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="C25" s="9">
         <v>2022</v>
@@ -1385,24 +1302,20 @@
         <v>1.33</v>
       </c>
       <c r="H25" s="10">
-        <f>F25*G25/(1-$B$2)</f>
-        <v>4994.079687815217</v>
-      </c>
-      <c r="I25" s="10">
-        <f>H25*$B$3</f>
+        <f>F25*G25/(1-$B$2)*$B$3</f>
         <v>399.52637502521736</v>
       </c>
-      <c r="J25" s="12">
-        <f>H25+I25</f>
+      <c r="I25" s="12">
+        <f>F25*G25/(1-$B$2)*(1+$B$3)</f>
         <v>5393.606062840435</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="4">
         <v>2022</v>
@@ -1421,24 +1334,20 @@
         <v>1.25</v>
       </c>
       <c r="H26" s="5">
-        <f>F26*G26/(1-$B$2)</f>
-        <v>5312.675808423912</v>
-      </c>
-      <c r="I26" s="5">
-        <f>H26*$B$3</f>
+        <f>F26*G26/(1-$B$2)*$B$3</f>
         <v>425.01406467391297</v>
       </c>
-      <c r="J26" s="7">
-        <f>H26+I26</f>
+      <c r="I26" s="7">
+        <f>F26*G26/(1-$B$2)*(1+$B$3)</f>
         <v>5737.6898730978255</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="9">
         <v>2022</v>
@@ -1457,24 +1366,20 @@
         <v>1.25</v>
       </c>
       <c r="H27" s="10">
-        <f>F27*G27/(1-$B$2)</f>
-        <v>5578.759257472825</v>
-      </c>
-      <c r="I27" s="10">
-        <f>H27*$B$3</f>
+        <f>F27*G27/(1-$B$2)*$B$3</f>
         <v>446.300740597826</v>
       </c>
-      <c r="J27" s="12">
-        <f>H27+I27</f>
+      <c r="I27" s="12">
+        <f>F27*G27/(1-$B$2)*(1+$B$3)</f>
         <v>6025.059998070651</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
         <v>47</v>
-      </c>
-      <c r="B28" t="s">
-        <v>48</v>
       </c>
       <c r="C28" s="4">
         <v>2019</v>
@@ -1493,24 +1398,20 @@
         <v>1.25</v>
       </c>
       <c r="H28" s="5">
-        <f>F28*G28/(1-$B$2)</f>
-        <v>5988.471847826087</v>
-      </c>
-      <c r="I28" s="5">
-        <f>H28*$B$3</f>
+        <f>F28*G28/(1-$B$2)*$B$3</f>
         <v>479.0777478260869</v>
       </c>
-      <c r="J28" s="7">
-        <f>H28+I28</f>
+      <c r="I28" s="7">
+        <f>F28*G28/(1-$B$2)*(1+$B$3)</f>
         <v>6467.549595652174</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="C29" s="9">
         <v>2020</v>
@@ -1529,24 +1430,20 @@
         <v>1.25</v>
       </c>
       <c r="H29" s="10">
-        <f>F29*G29/(1-$B$2)</f>
-        <v>6766.021546874999</v>
-      </c>
-      <c r="I29" s="10">
-        <f>H29*$B$3</f>
+        <f>F29*G29/(1-$B$2)*$B$3</f>
         <v>541.28172375</v>
       </c>
-      <c r="J29" s="12">
-        <f>H29+I29</f>
+      <c r="I29" s="12">
+        <f>F29*G29/(1-$B$2)*(1+$B$3)</f>
         <v>7307.303270625</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" t="s">
         <v>51</v>
-      </c>
-      <c r="B30" t="s">
-        <v>52</v>
       </c>
       <c r="C30" s="4">
         <v>2016</v>
@@ -1565,24 +1462,20 @@
         <v>1.25</v>
       </c>
       <c r="H30" s="5">
-        <f>F30*G30/(1-$B$2)</f>
-        <v>6912.10337160326</v>
-      </c>
-      <c r="I30" s="5">
-        <f>H30*$B$3</f>
+        <f>F30*G30/(1-$B$2)*$B$3</f>
         <v>552.9682697282608</v>
       </c>
-      <c r="J30" s="7">
-        <f>H30+I30</f>
+      <c r="I30" s="7">
+        <f>F30*G30/(1-$B$2)*(1+$B$3)</f>
         <v>7465.071641331521</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="C31" s="9">
         <v>2023</v>
@@ -1601,24 +1494,20 @@
         <v>1.2</v>
       </c>
       <c r="H31" s="10">
-        <f>F31*G31/(1-$B$2)</f>
-        <v>7202.773827391304</v>
-      </c>
-      <c r="I31" s="10">
-        <f>H31*$B$3</f>
+        <f>F31*G31/(1-$B$2)*$B$3</f>
         <v>576.2219061913044</v>
       </c>
-      <c r="J31" s="12">
-        <f>H31+I31</f>
+      <c r="I31" s="12">
+        <f>F31*G31/(1-$B$2)*(1+$B$3)</f>
         <v>7778.995733582608</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="4">
         <v>2023</v>
@@ -1637,24 +1526,20 @@
         <v>1.2</v>
       </c>
       <c r="H32" s="5">
-        <f>F32*G32/(1-$B$2)</f>
-        <v>9430.673720869563</v>
-      </c>
-      <c r="I32" s="5">
-        <f>H32*$B$3</f>
+        <f>F32*G32/(1-$B$2)*$B$3</f>
         <v>754.4538976695651</v>
       </c>
-      <c r="J32" s="7">
-        <f>H32+I32</f>
+      <c r="I32" s="7">
+        <f>F32*G32/(1-$B$2)*(1+$B$3)</f>
         <v>10185.127618539129</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="C33" s="9">
         <v>2006</v>
@@ -1673,24 +1558,20 @@
         <v>1.2</v>
       </c>
       <c r="H33" s="10">
-        <f>F33*G33/(1-$B$2)</f>
-        <v>10886.39823521739</v>
-      </c>
-      <c r="I33" s="10">
-        <f>H33*$B$3</f>
+        <f>F33*G33/(1-$B$2)*$B$3</f>
         <v>870.9118588173912</v>
       </c>
-      <c r="J33" s="12">
-        <f>H33+I33</f>
+      <c r="I33" s="12">
+        <f>F33*G33/(1-$B$2)*(1+$B$3)</f>
         <v>11757.310094034781</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" t="s">
         <v>58</v>
-      </c>
-      <c r="B34" t="s">
-        <v>59</v>
       </c>
       <c r="C34" s="4">
         <v>2022</v>
@@ -1709,20 +1590,16 @@
         <v>1.2</v>
       </c>
       <c r="H34" s="5">
-        <f>F34*G34/(1-$B$2)</f>
-        <v>11024.17233065217</v>
-      </c>
-      <c r="I34" s="5">
-        <f>H34*$B$3</f>
+        <f>F34*G34/(1-$B$2)*$B$3</f>
         <v>881.9337864521736</v>
       </c>
-      <c r="J34" s="7">
-        <f>H34+I34</f>
+      <c r="I34" s="7">
+        <f>F34*G34/(1-$B$2)*(1+$B$3)</f>
         <v>11906.106117104346</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J34"/>
+  <autoFilter ref="A5:I34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
